--- a/feedback_forms/009_photo_feedback_and_personality_survey--feedback_forms.xlsx
+++ b/feedback_forms/009_photo_feedback_and_personality_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Agreeableness Likertscale</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Conscientiousness Likertscale</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Neuroticism Likertscale</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>extraversion_likertscale</t>
+          <t>extraversion_likertscale_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Extraversion Likertscale 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How good is this survey?</t>
+          <t>Survey Rating Likertscale</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{1:_'agreeable'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1: 'Agreeable'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{2:_'conscientious'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{2: 'Conscientious'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{3:_'neurotic'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{3: 'Neurotic'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{1:_'male'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{1: 'Male'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{2:_'female'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{2: 'Female'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{3:_'other'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{3: 'Other'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{1:_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{1: True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{2:_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{2: False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
